--- a/Dax_Dataset/Dax_1.xlsx
+++ b/Dax_Dataset/Dax_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\Power-BI\Dax_Dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB0EEBC-1F5D-493A-8C51-D34CAB838647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1076A62-6125-4C4A-A761-BA2A95553B36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{7EBB94DD-F6BF-47AF-9900-FE31ECA3A549}"/>
   </bookViews>
@@ -60,40 +60,40 @@
     <t>SalesAmount</t>
   </si>
   <si>
+    <t>West</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>Electronics</t>
+  </si>
+  <si>
+    <t>East</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>Accessories</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>Keyboard</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>Headphones</t>
+  </si>
+  <si>
     <t>Cost</t>
-  </si>
-  <si>
-    <t>West</t>
-  </si>
-  <si>
-    <t>Laptop</t>
-  </si>
-  <si>
-    <t>Electronics</t>
-  </si>
-  <si>
-    <t>East</t>
-  </si>
-  <si>
-    <t>Mouse</t>
-  </si>
-  <si>
-    <t>Accessories</t>
-  </si>
-  <si>
-    <t>North</t>
-  </si>
-  <si>
-    <t>Keyboard</t>
-  </si>
-  <si>
-    <t>South</t>
-  </si>
-  <si>
-    <t>Monitor</t>
-  </si>
-  <si>
-    <t>Headphones</t>
   </si>
 </sst>
 </file>
@@ -450,6 +450,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -476,7 +478,7 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -487,13 +489,13 @@
         <v>45296</v>
       </c>
       <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -513,13 +515,13 @@
         <v>45303</v>
       </c>
       <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -539,13 +541,13 @@
         <v>45325</v>
       </c>
       <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
         <v>14</v>
       </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -565,13 +567,13 @@
         <v>45340</v>
       </c>
       <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
         <v>16</v>
       </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -591,13 +593,13 @@
         <v>45358</v>
       </c>
       <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
         <v>8</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>9</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -617,13 +619,13 @@
         <v>45373</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F7">
         <v>4</v>
@@ -643,13 +645,13 @@
         <v>45384</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8">
         <v>3</v>
@@ -669,13 +671,13 @@
         <v>45397</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -695,13 +697,13 @@
         <v>45421</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F10">
         <v>4</v>
@@ -721,13 +723,13 @@
         <v>45433</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" t="s">
         <v>9</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
       </c>
       <c r="F11">
         <v>2</v>
@@ -747,13 +749,13 @@
         <v>45447</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -773,13 +775,13 @@
         <v>45462</v>
       </c>
       <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
         <v>16</v>
       </c>
-      <c r="D13" t="s">
-        <v>17</v>
-      </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -799,13 +801,13 @@
         <v>45481</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F14">
         <v>6</v>
@@ -825,13 +827,13 @@
         <v>45496</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F15">
         <v>2</v>
@@ -851,13 +853,13 @@
         <v>45515</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D16" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" t="s">
         <v>9</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
       </c>
       <c r="F16">
         <v>3</v>
@@ -877,13 +879,13 @@
         <v>45530</v>
       </c>
       <c r="C17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F17">
         <v>3</v>
@@ -903,13 +905,13 @@
         <v>45540</v>
       </c>
       <c r="C18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F18">
         <v>4</v>
@@ -929,13 +931,13 @@
         <v>45552</v>
       </c>
       <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" t="s">
         <v>11</v>
       </c>
-      <c r="D19" t="s">
-        <v>12</v>
-      </c>
       <c r="E19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F19">
         <v>4</v>
@@ -955,13 +957,13 @@
         <v>45571</v>
       </c>
       <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
         <v>14</v>
       </c>
-      <c r="D20" t="s">
-        <v>15</v>
-      </c>
       <c r="E20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -981,13 +983,13 @@
         <v>45585</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" t="s">
         <v>9</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -1007,13 +1009,13 @@
         <v>45599</v>
       </c>
       <c r="C22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F22">
         <v>6</v>
@@ -1033,13 +1035,13 @@
         <v>45610</v>
       </c>
       <c r="C23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F23">
         <v>2</v>
@@ -1059,13 +1061,13 @@
         <v>45628</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F24">
         <v>10</v>
@@ -1085,13 +1087,13 @@
         <v>45644</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F25">
         <v>3</v>
@@ -1111,13 +1113,13 @@
         <v>45664</v>
       </c>
       <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" t="s">
         <v>8</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>9</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
       </c>
       <c r="F26">
         <v>2</v>
@@ -1137,13 +1139,13 @@
         <v>45700</v>
       </c>
       <c r="C27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F27">
         <v>5</v>
@@ -1163,13 +1165,13 @@
         <v>45732</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F28">
         <v>3</v>
@@ -1189,13 +1191,13 @@
         <v>45829</v>
       </c>
       <c r="C29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F29">
         <v>7</v>
@@ -1215,13 +1217,13 @@
         <v>45909</v>
       </c>
       <c r="C30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F30">
         <v>4</v>
@@ -1241,13 +1243,13 @@
         <v>46006</v>
       </c>
       <c r="C31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D31" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" t="s">
         <v>9</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
       </c>
       <c r="F31">
         <v>3</v>

--- a/Dax_Dataset/Dax_1.xlsx
+++ b/Dax_Dataset/Dax_1.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\Power-BI\Dax_Dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1076A62-6125-4C4A-A761-BA2A95553B36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E925AFBB-6217-49F0-9517-EDA3E4F54132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{7EBB94DD-F6BF-47AF-9900-FE31ECA3A549}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sales" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
